--- a/ECAD/interconnects/reference/OH-PL-INTERCONNECT_A_v5.xlsx
+++ b/ECAD/interconnects/reference/OH-PL-INTERCONNECT_A_v5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OpenHornet\ECAD\interconnects\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C470305D-13E1-4619-809A-10CAAAB0CD64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E226B9C0-3D72-4973-ABFF-3459D5CE45A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13605" yWindow="1110" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OH-PL-INTERCONNECT_-_v1" sheetId="1" r:id="rId1"/>
@@ -638,12 +638,6 @@
     <t>4A13A1W1</t>
   </si>
   <si>
-    <t>1589-01C</t>
-  </si>
-  <si>
-    <t>CABLE, USB-B PNL MNT RCPT TO USB-A, USB 2.0, 1' L</t>
-  </si>
-  <si>
     <t>4A14A1W1</t>
   </si>
   <si>
@@ -806,12 +800,6 @@
     <t>CABLE, USB-A PNL MNT RCPT TO USB-A, USB 3.0, 4' L</t>
   </si>
   <si>
-    <t>2024-09-09</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>1A2W1P3, 1A6W1P3, 1A7W1P3, 1A7W2P4, 2A2A1W1P3, 2A2A1W1P4, 2A4A1W1P3, 2A4A1W2P4, 2A5A1W1P4, 2A5A1W2P3, 3A2A1W1P3, 3A2A1W2P4, 4A2A1W1P3, 4A3A1W1P3, 4A3A1W2P4, 4A3A3W1P3, 4A3A3W2P4, 4A4A2W1P3, 4A5A1A1W1P1, 4A5A2W1P4, 4A6A1W1P4, 4A7A2W1P1, 5A2W1P3, 5A2W1P4, 5A4A1W1P3, 5A4A1W2P3, 5A5A1W1P3, 5A5A1W2P4, 5A6A1P3, 5A6A1P4, 5A7A1W1P3, 5A7A1W2P4, 5A8A1W1P3, 5A8A1W2P4, 5A9A1W1P3, 5A9A1W2P4, 5A10W1P3, 5A10W1P4</t>
   </si>
   <si>
@@ -831,6 +819,18 @@
   </si>
   <si>
     <t>3A2A1W1J3, 3A2A1W2J1, 3A2A1W2J2, 4A4A2W1J1, 4A4A2W1J2, 4A5A2W2P2, 4A7A2W1J2, 5A2W1P7</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>2026/09/19</t>
+  </si>
+  <si>
+    <t>1689-01C</t>
+  </si>
+  <si>
+    <t>CABLE, USB-B PNL MNT RCPT TO USB-A, USB 3.0, 1' L</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1371,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1379,30 +1379,27 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1697,9 +1694,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1737,7 +1734,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1843,7 +1840,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1985,7 +1982,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2006,70 +2003,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B3" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="E1" s="7"/>
-    </row>
-    <row r="2" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="C4" s="8"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>247</v>
-      </c>
       <c r="B5" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="C5" s="17"/>
+        <v>263</v>
+      </c>
+      <c r="C5" s="8"/>
       <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2083,10 +2080,10 @@
         <v>3814</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,7 +2094,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>40</v>
@@ -2114,7 +2111,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>42</v>
@@ -2131,7 +2128,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>48</v>
@@ -2148,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>46</v>
@@ -2165,7 +2162,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>162</v>
@@ -2182,13 +2179,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>201</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2199,13 +2196,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>207</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2267,13 +2264,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2284,10 +2281,10 @@
         <v>66</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>126</v>
@@ -2301,10 +2298,10 @@
         <v>8</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>149</v>
@@ -2318,10 +2315,10 @@
         <v>2</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>99</v>
@@ -2335,10 +2332,10 @@
         <v>8</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>137</v>
@@ -2352,10 +2349,10 @@
         <v>44</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>15</v>
@@ -2369,13 +2366,13 @@
         <v>12</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>234</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2505,13 +2502,13 @@
         <v>73</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>221</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2556,13 +2553,13 @@
         <v>1</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>187</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2777,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="15" t="s">
         <v>211</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2970,7 +2967,7 @@
         <v>66</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3004,7 +3001,7 @@
         <v>45</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3050,13 +3047,13 @@
         <v>749</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3254,13 +3251,13 @@
         <v>136</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3277,7 +3274,7 @@
         <v>171</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -3362,7 +3359,7 @@
         <v>173</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -3441,13 +3438,13 @@
         <v>134</v>
       </c>
       <c r="C87" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E87" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E87" s="15" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="60" x14ac:dyDescent="0.25">
@@ -3458,13 +3455,13 @@
         <v>127</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
